--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_ambatoharanana.xlsx
@@ -432,9 +432,6 @@
           <t>Ouvert</t>
         </is>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -451,9 +448,6 @@
         <is>
           <t>Mefiant</t>
         </is>
-      </c>
-      <c r="D5">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
